--- a/public/templates/office/EMP_DEG_140_CRUD_Matrix.xlsx
+++ b/public/templates/office/EMP_DEG_140_CRUD_Matrix.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\내 드라이브\00. 엠파시\08. 프로젝트\010. 진행중\한빛글로벌\syncguard_ai\3.설계 (Design)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\내 드라이브\00. 엠파시\08. 프로젝트\010. 진행중\한빛글로벌\syncflow_ai\3.설계 (Design)\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C5B344C-A009-4557-9CC8-D80279C4423D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -43,7 +43,7 @@
     <t>프로젝트명</t>
   </si>
   <si>
-    <t>한빛글로벌 SyncGuard AI 시스템 구축</t>
+    <t>한빛글로벌 SyncFlow AI 시스템 구축</t>
   </si>
   <si>
     <t>최종작성일</t>
@@ -100,13 +100,13 @@
     <t>초기 제정</t>
   </si>
   <si>
-    <t>SyncGuard AI 착수보고서(v1.4) 및 로컬 설계 기준 최초 작성</t>
+    <t>SyncFlow AI 착수보고서(v1.4) 및 로컬 설계 기준 최초 작성</t>
   </si>
   <si>
     <t>엠파시</t>
   </si>
   <si>
-    <t>한빛글로벌 RA</t>
+    <t>한빛글로벌 QA</t>
   </si>
   <si>
     <t>개정 사유   제정 또는 개정 내용이 이전 문서에 대해 추가/수정/삭제인지 선택 기입</t>
@@ -119,58 +119,58 @@
     단위프로세스</t>
   </si>
   <si>
-    <t>review_request</t>
-  </si>
-  <si>
-    <t>review_document</t>
-  </si>
-  <si>
-    <t>review_sentence</t>
-  </si>
-  <si>
-    <t>review_rule_dict</t>
-  </si>
-  <si>
-    <t>syncguard_ai_analysis</t>
-  </si>
-  <si>
-    <t>review_ra_review</t>
-  </si>
-  <si>
-    <t>review_evidence</t>
-  </si>
-  <si>
-    <t>review_history_immutable</t>
-  </si>
-  <si>
-    <t>review_regulation_doc</t>
-  </si>
-  <si>
-    <t>review_regulation_chunk</t>
-  </si>
-  <si>
-    <t>review_prompt_template</t>
-  </si>
-  <si>
-    <t>review_golden_set</t>
-  </si>
-  <si>
-    <t>review_golden_set_item</t>
-  </si>
-  <si>
-    <t>review_eval_log</t>
-  </si>
-  <si>
-    <t>review_mkthub_log</t>
-  </si>
-  <si>
-    <t>review_lemon_log</t>
-  </si>
-  <si>
-    <t>review_ingredient</t>
-  </si>
-  <si>
-    <t>시안·동영상 캡처 장면 등록 및 마케팅허브 의뢰 접수 (F-01, 19, 20, 36)</t>
+    <t>verify_request</t>
+  </si>
+  <si>
+    <t>verify_document</t>
+  </si>
+  <si>
+    <t>verify_sentence</t>
+  </si>
+  <si>
+    <t>verify_rule_dict</t>
+  </si>
+  <si>
+    <t>syncflow_ai_analysis</t>
+  </si>
+  <si>
+    <t>verify_ra_review</t>
+  </si>
+  <si>
+    <t>verify_evidence</t>
+  </si>
+  <si>
+    <t>verify_history_immutable</t>
+  </si>
+  <si>
+    <t>verify_regulation_doc</t>
+  </si>
+  <si>
+    <t>verify_regulation_chunk</t>
+  </si>
+  <si>
+    <t>verify_prompt_template</t>
+  </si>
+  <si>
+    <t>verify_golden_set</t>
+  </si>
+  <si>
+    <t>verify_golden_set_item</t>
+  </si>
+  <si>
+    <t>verify_eval_log</t>
+  </si>
+  <si>
+    <t>verify_srm-portal_log</t>
+  </si>
+  <si>
+    <t>verify_lemon_log</t>
+  </si>
+  <si>
+    <t>verify_ingredient</t>
+  </si>
+  <si>
+    <t>계약서·설계도면 스냅샷 장면 등록 및 전자구매포털 의뢰 접수 (F-01, 19, 20, 36)</t>
   </si>
   <si>
     <t>C</t>
@@ -197,22 +197,22 @@
     <t>3단계 AI 판정 실행 (F-07~16)</t>
   </si>
   <si>
-    <t>실증 자료 검증 및 매핑 (F-13, 27)</t>
-  </si>
-  <si>
-    <t>RA 전문가 심의 및 최종 확정 (F-28, 29)</t>
+    <t>시험성적서 검증 및 매핑 (F-13, 27)</t>
+  </si>
+  <si>
+    <t>법무·QA 전문위원 검증 및 최종 확정 (F-28, 29)</t>
   </si>
   <si>
     <t>U</t>
   </si>
   <si>
-    <t>심의 결과 통보 및 MarketingHub 회신 (F-24, 36)</t>
+    <t>검증 결과 통보 및 SRM-Portal 회신 (F-24, 36)</t>
   </si>
   <si>
     <t>골든셋 평가 및 품질 관리 (F-31~34)</t>
   </si>
   <si>
-    <t>ProductLab 전성분·실증 동기화 및 [Option] KT 레몬 연계 (F-37)</t>
+    <t>PLM-Nexus 자재BOM·시험검증 동기화 및 [Option] HB-Monitor 연계 (F-37)</t>
   </si>
   <si>
     <t>사용자 권한 및 공통코드 관리 (F-17, 38, 43)</t>
